--- a/csv/policies/turn off/Off_OBPS/formula_Off_OBPS_SK.xlsx
+++ b/csv/policies/turn off/Off_OBPS/formula_Off_OBPS_SK.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,12 +440,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
